--- a/Reports/ForPopulation/InformationBill_UK_QrCode/InformationBill_UK_QrCode.xlsx
+++ b/Reports/ForPopulation/InformationBill_UK_QrCode/InformationBill_UK_QrCode.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS-test\Reports\ForPopulation\InformationBill_UK_QrCode\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\ForPopulation\InformationBill_UK_QrCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{493DF05E-B9B3-4D1E-9F15-B77C8D428764}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AC37B9-6A13-4DAC-81C3-38920E8C6305}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="77">
   <si>
     <t>Width</t>
   </si>
@@ -244,10 +244,13 @@
     <t>$QrCODE_this-&gt;H['QR_MainChannel']</t>
   </si>
   <si>
-    <t>$t1['QR_MainChannel']</t>
-  </si>
-  <si>
     <t>Чат дома</t>
+  </si>
+  <si>
+    <t>$this-&gt;H['QR_HomeChannel'] =$t1['QR_HomeChannel']</t>
+  </si>
+  <si>
+    <t>$QrCODE_this-&gt;H['QR_HomeChannel']</t>
   </si>
 </sst>
 </file>
@@ -635,7 +638,42 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -661,42 +699,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1056,18 +1059,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="59" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
+      <c r="B1" s="60"/>
+      <c r="C1" s="60"/>
+      <c r="D1" s="60"/>
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="60"/>
+      <c r="H1" s="60"/>
+      <c r="I1" s="60"/>
+      <c r="J1" s="60"/>
       <c r="K1" s="27"/>
       <c r="L1" t="s">
         <v>0</v>
@@ -1086,35 +1089,35 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A2" s="55" t="s">
+      <c r="A2" s="45" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="55" t="s">
+      <c r="C2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="56"/>
-      <c r="E2" s="56"/>
-      <c r="F2" s="56"/>
-      <c r="G2" s="56"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-      <c r="J2" s="56"/>
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
+      <c r="I2" s="46"/>
+      <c r="J2" s="46"/>
       <c r="K2" s="29"/>
     </row>
     <row r="3" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A3" s="55"/>
+      <c r="A3" s="45"/>
       <c r="B3" s="36"/>
-      <c r="C3" s="56"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="56"/>
-      <c r="G3" s="56"/>
-      <c r="H3" s="56"/>
-      <c r="I3" s="56"/>
-      <c r="J3" s="56"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="46"/>
+      <c r="E3" s="46"/>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
+      <c r="I3" s="46"/>
+      <c r="J3" s="46"/>
       <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:22" ht="11.1" customHeight="1">
@@ -1151,7 +1154,9 @@
       <c r="J5" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="K5" s="6"/>
+      <c r="K5" s="5" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="6" spans="1:22" ht="11.1" customHeight="1">
       <c r="A6" s="17" t="s">
@@ -1161,9 +1166,6 @@
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
-      <c r="F6" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="G6" s="4" t="s">
         <v>10</v>
       </c>
@@ -1203,49 +1205,49 @@
       <c r="A8" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="59" t="s">
+      <c r="B8" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="57" t="s">
+      <c r="C8" s="50"/>
+      <c r="D8" s="47" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="57" t="s">
+      <c r="E8" s="47" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="57" t="s">
+      <c r="F8" s="47" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="57" t="s">
+      <c r="G8" s="47" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="47" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="59" t="s">
+      <c r="I8" s="49" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="60"/>
+      <c r="J8" s="50"/>
       <c r="K8" s="30"/>
     </row>
     <row r="9" spans="1:22" ht="11.1" customHeight="1">
       <c r="A9" s="28"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="62"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="61"/>
-      <c r="J9" s="62"/>
+      <c r="B9" s="51"/>
+      <c r="C9" s="52"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="51"/>
+      <c r="J9" s="52"/>
       <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:22" ht="11.1" customHeight="1">
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="61" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="51"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="35" t="s">
         <v>53</v>
       </c>
@@ -1261,10 +1263,10 @@
       <c r="H10" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="52" t="s">
+      <c r="I10" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="53"/>
+      <c r="J10" s="64"/>
       <c r="K10" s="30"/>
       <c r="M10" s="8" t="s">
         <v>1</v>
@@ -1281,12 +1283,12 @@
       <c r="Q10" s="9"/>
     </row>
     <row r="11" spans="1:22" ht="11.1" customHeight="1">
-      <c r="B11" s="42" t="s">
+      <c r="B11" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="54"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="54"/>
+      <c r="C11" s="65"/>
+      <c r="D11" s="65"/>
+      <c r="E11" s="65"/>
       <c r="F11" s="14"/>
       <c r="G11" s="15" t="s">
         <v>27</v>
@@ -1294,10 +1296,10 @@
       <c r="H11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="43" t="s">
+      <c r="I11" s="54" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="54"/>
+      <c r="J11" s="65"/>
       <c r="K11" s="31"/>
       <c r="M11" s="10" t="s">
         <v>30</v>
@@ -1346,53 +1348,53 @@
     </row>
     <row r="13" spans="1:22" ht="11.1" customHeight="1">
       <c r="A13" s="18"/>
-      <c r="B13" s="42" t="s">
+      <c r="B13" s="53" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="43" t="s">
+      <c r="C13" s="53"/>
+      <c r="D13" s="53"/>
+      <c r="E13" s="53"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="53"/>
+      <c r="H13" s="53"/>
+      <c r="I13" s="54" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="44"/>
+      <c r="J13" s="55"/>
       <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:22" ht="11.1" customHeight="1">
       <c r="A14" s="19"/>
-      <c r="B14" s="42" t="s">
+      <c r="B14" s="53" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="42"/>
-      <c r="D14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="42"/>
-      <c r="G14" s="42"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="43" t="s">
+      <c r="C14" s="53"/>
+      <c r="D14" s="53"/>
+      <c r="E14" s="53"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="53"/>
+      <c r="H14" s="53"/>
+      <c r="I14" s="54" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="44"/>
+      <c r="J14" s="55"/>
       <c r="K14" s="24"/>
     </row>
     <row r="15" spans="1:22" ht="11.1" customHeight="1">
       <c r="A15" s="19"/>
-      <c r="B15" s="42" t="s">
+      <c r="B15" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="43" t="s">
+      <c r="C15" s="53"/>
+      <c r="D15" s="53"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="53"/>
+      <c r="H15" s="53"/>
+      <c r="I15" s="54" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="44"/>
+      <c r="J15" s="55"/>
       <c r="K15" s="24"/>
       <c r="M15" s="12" t="s">
         <v>36</v>
@@ -1403,19 +1405,19 @@
     </row>
     <row r="16" spans="1:22" ht="11.1" customHeight="1">
       <c r="A16" s="19"/>
-      <c r="B16" s="42" t="s">
+      <c r="B16" s="53" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="42"/>
-      <c r="D16" s="42"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="42"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="43" t="s">
+      <c r="C16" s="53"/>
+      <c r="D16" s="53"/>
+      <c r="E16" s="53"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="53"/>
+      <c r="H16" s="53"/>
+      <c r="I16" s="54" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="44"/>
+      <c r="J16" s="55"/>
       <c r="K16" s="24"/>
       <c r="M16" s="12" t="s">
         <v>34</v>
@@ -1438,19 +1440,19 @@
     </row>
     <row r="17" spans="1:22" ht="11.1" customHeight="1">
       <c r="A17" s="19"/>
-      <c r="B17" s="42" t="s">
+      <c r="B17" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="42"/>
-      <c r="D17" s="42"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="43" t="s">
+      <c r="C17" s="53"/>
+      <c r="D17" s="53"/>
+      <c r="E17" s="53"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="53"/>
+      <c r="H17" s="53"/>
+      <c r="I17" s="54" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="44"/>
+      <c r="J17" s="55"/>
       <c r="K17" s="24"/>
       <c r="M17" s="12" t="s">
         <v>34</v>
@@ -1480,17 +1482,17 @@
     </row>
     <row r="19" spans="1:22" ht="11.1" customHeight="1">
       <c r="A19" s="25"/>
-      <c r="B19" s="45" t="s">
+      <c r="B19" s="56" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="47"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="58"/>
       <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:22" ht="11.1" customHeight="1">
@@ -1511,20 +1513,20 @@
         <v>73</v>
       </c>
       <c r="F21" s="40" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="41.45" customHeight="1">
-      <c r="C22" s="64" t="s">
+      <c r="C22" s="42" t="s">
         <v>71</v>
       </c>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
-      <c r="F22" s="65" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="41"/>
+      <c r="F22" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
       <c r="M22" s="12" t="s">
         <v>36</v>
       </c>
@@ -1630,121 +1632,121 @@
     </row>
     <row r="46" spans="2:6" ht="11.1" customHeight="1">
       <c r="B46" s="13"/>
-      <c r="C46" s="41" t="s">
+      <c r="C46" s="66" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
+      <c r="D46" s="66"/>
+      <c r="E46" s="66"/>
+      <c r="F46" s="66"/>
     </row>
     <row r="47" spans="2:6" ht="11.1" customHeight="1">
       <c r="B47" s="13"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="66"/>
+      <c r="E47" s="66"/>
+      <c r="F47" s="66"/>
     </row>
     <row r="48" spans="2:6" ht="11.1" customHeight="1">
       <c r="B48" s="13"/>
-      <c r="C48" s="41" t="s">
+      <c r="C48" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
+      <c r="D48" s="66"/>
+      <c r="E48" s="66"/>
+      <c r="F48" s="66"/>
     </row>
     <row r="49" spans="2:6" ht="11.1" customHeight="1">
       <c r="B49" s="13"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
+      <c r="C49" s="66"/>
+      <c r="D49" s="66"/>
+      <c r="E49" s="66"/>
+      <c r="F49" s="66"/>
     </row>
     <row r="50" spans="2:6" ht="11.1" customHeight="1">
       <c r="B50" s="13"/>
-      <c r="C50" s="41" t="s">
+      <c r="C50" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
+      <c r="D50" s="66"/>
+      <c r="E50" s="66"/>
+      <c r="F50" s="66"/>
     </row>
     <row r="51" spans="2:6" ht="11.1" customHeight="1">
       <c r="B51" s="13"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="66"/>
+      <c r="E51" s="66"/>
+      <c r="F51" s="66"/>
     </row>
     <row r="52" spans="2:6" ht="11.1" customHeight="1">
       <c r="B52" s="13"/>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="66"/>
+      <c r="E52" s="66"/>
+      <c r="F52" s="66"/>
     </row>
     <row r="53" spans="2:6" ht="11.1" customHeight="1">
       <c r="B53" s="13"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
+      <c r="C53" s="66"/>
+      <c r="D53" s="66"/>
+      <c r="E53" s="66"/>
+      <c r="F53" s="66"/>
     </row>
     <row r="54" spans="2:6" ht="11.1" customHeight="1">
       <c r="B54" s="13"/>
-      <c r="C54" s="41"/>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
+      <c r="C54" s="66"/>
+      <c r="D54" s="66"/>
+      <c r="E54" s="66"/>
+      <c r="F54" s="66"/>
     </row>
     <row r="55" spans="2:6" ht="11.1" customHeight="1">
       <c r="B55" s="13"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
+      <c r="C55" s="66"/>
+      <c r="D55" s="66"/>
+      <c r="E55" s="66"/>
+      <c r="F55" s="66"/>
     </row>
     <row r="56" spans="2:6" ht="11.1" customHeight="1">
       <c r="B56" s="13"/>
-      <c r="C56" s="41"/>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
+      <c r="C56" s="66"/>
+      <c r="D56" s="66"/>
+      <c r="E56" s="66"/>
+      <c r="F56" s="66"/>
     </row>
     <row r="57" spans="2:6" ht="11.1" customHeight="1">
       <c r="B57" s="13"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
+      <c r="C57" s="66"/>
+      <c r="D57" s="66"/>
+      <c r="E57" s="66"/>
+      <c r="F57" s="66"/>
     </row>
     <row r="58" spans="2:6" ht="11.1" customHeight="1">
       <c r="B58" s="13"/>
-      <c r="C58" s="41"/>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
+      <c r="C58" s="66"/>
+      <c r="D58" s="66"/>
+      <c r="E58" s="66"/>
+      <c r="F58" s="66"/>
     </row>
     <row r="59" spans="2:6" ht="11.1" customHeight="1">
       <c r="B59" s="13"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
+      <c r="C59" s="66"/>
+      <c r="D59" s="66"/>
+      <c r="E59" s="66"/>
+      <c r="F59" s="66"/>
     </row>
     <row r="60" spans="2:6" ht="11.1" customHeight="1">
       <c r="B60" s="13"/>
-      <c r="C60" s="41"/>
-      <c r="D60" s="41"/>
-      <c r="E60" s="41"/>
-      <c r="F60" s="41"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="66"/>
     </row>
     <row r="61" spans="2:6" ht="11.1" customHeight="1">
       <c r="B61" s="13"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="41"/>
-      <c r="E61" s="41"/>
-      <c r="F61" s="41"/>
+      <c r="C61" s="66"/>
+      <c r="D61" s="66"/>
+      <c r="E61" s="66"/>
+      <c r="F61" s="66"/>
     </row>
     <row r="62" spans="2:6" ht="11.1" customHeight="1">
       <c r="B62" s="13"/>
@@ -1757,6 +1759,25 @@
     </row>
   </sheetData>
   <mergeCells count="34">
+    <mergeCell ref="C56:F57"/>
+    <mergeCell ref="C58:F59"/>
+    <mergeCell ref="C60:F61"/>
+    <mergeCell ref="C46:F47"/>
+    <mergeCell ref="C48:F49"/>
+    <mergeCell ref="C50:F51"/>
+    <mergeCell ref="C52:F53"/>
+    <mergeCell ref="C54:F55"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="I11:J11"/>
     <mergeCell ref="F22:H22"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:J3"/>
@@ -1770,27 +1791,8 @@
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="B19:J19"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:J13"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="I17:J17"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="C56:F57"/>
-    <mergeCell ref="C58:F59"/>
-    <mergeCell ref="C60:F61"/>
-    <mergeCell ref="C46:F47"/>
-    <mergeCell ref="C48:F49"/>
-    <mergeCell ref="C50:F51"/>
-    <mergeCell ref="C52:F53"/>
-    <mergeCell ref="C54:F55"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.27559055118110237" bottom="0.27559055118110237" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="10000" orientation="portrait" r:id="rId1"/>

--- a/Reports/ForPopulation/InformationBill_UK_QrCode/InformationBill_UK_QrCode.xlsx
+++ b/Reports/ForPopulation/InformationBill_UK_QrCode/InformationBill_UK_QrCode.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\ForPopulation\InformationBill_UK_QrCode\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AC37B9-6A13-4DAC-81C3-38920E8C6305}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91EAE2D5-0F2A-4B24-BC46-68BF96476402}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="45" windowWidth="28560" windowHeight="12600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -235,9 +235,6 @@
     <t>Перерасчет руб.</t>
   </si>
   <si>
-    <t>Официальный канал в МАХ</t>
-  </si>
-  <si>
     <t>$this-&gt;H['QR_MainChannel'] =$t1['QR_MainChannel']</t>
   </si>
   <si>
@@ -251,6 +248,9 @@
   </si>
   <si>
     <t>$QrCODE_this-&gt;H['QR_HomeChannel']</t>
+  </si>
+  <si>
+    <t>"Канал УК ".$this-&gt;H['name_organization']</t>
   </si>
 </sst>
 </file>
@@ -260,7 +260,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.00_ ;[Red]\-#,##0.00\ "/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -397,6 +397,19 @@
       <color rgb="FF6A8759"/>
       <name val="JetBrains Mono"/>
       <family val="3"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="204"/>
     </font>
   </fonts>
@@ -438,7 +451,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -568,11 +581,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
@@ -635,71 +710,73 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="2" fontId="18" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -1059,18 +1136,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
-      <c r="I1" s="60"/>
-      <c r="J1" s="60"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
+      <c r="G1" s="45"/>
+      <c r="H1" s="45"/>
+      <c r="I1" s="45"/>
+      <c r="J1" s="45"/>
       <c r="K1" s="27"/>
       <c r="L1" t="s">
         <v>0</v>
@@ -1089,35 +1166,35 @@
       </c>
     </row>
     <row r="2" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="54" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="45" t="s">
+      <c r="C2" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="46"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="46"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
       <c r="K2" s="29"/>
     </row>
     <row r="3" spans="1:22" ht="11.1" customHeight="1">
-      <c r="A3" s="45"/>
+      <c r="A3" s="54"/>
       <c r="B3" s="36"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="46"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
-      <c r="I3" s="46"/>
-      <c r="J3" s="46"/>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
+      <c r="I3" s="55"/>
+      <c r="J3" s="55"/>
       <c r="K3" s="29"/>
     </row>
     <row r="4" spans="1:22" ht="11.1" customHeight="1">
@@ -1136,7 +1213,7 @@
         <v>7</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="11.1" customHeight="1">
@@ -1155,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:22" ht="11.1" customHeight="1">
@@ -1205,49 +1282,49 @@
       <c r="A8" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="58" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="50"/>
-      <c r="D8" s="47" t="s">
+      <c r="C8" s="59"/>
+      <c r="D8" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="E8" s="47" t="s">
+      <c r="E8" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="56" t="s">
         <v>55</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="H8" s="47" t="s">
+      <c r="H8" s="56" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="49" t="s">
+      <c r="I8" s="58" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="50"/>
+      <c r="J8" s="59"/>
       <c r="K8" s="30"/>
     </row>
     <row r="9" spans="1:22" ht="11.1" customHeight="1">
       <c r="A9" s="28"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="52"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="52"/>
+      <c r="B9" s="60"/>
+      <c r="C9" s="61"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="60"/>
+      <c r="J9" s="61"/>
       <c r="K9" s="30"/>
     </row>
     <row r="10" spans="1:22" ht="11.1" customHeight="1">
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="62"/>
+      <c r="C10" s="50"/>
       <c r="D10" s="35" t="s">
         <v>53</v>
       </c>
@@ -1263,10 +1340,10 @@
       <c r="H10" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="63" t="s">
+      <c r="I10" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="64"/>
+      <c r="J10" s="52"/>
       <c r="K10" s="30"/>
       <c r="M10" s="8" t="s">
         <v>1</v>
@@ -1283,12 +1360,12 @@
       <c r="Q10" s="9"/>
     </row>
     <row r="11" spans="1:22" ht="11.1" customHeight="1">
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="65"/>
-      <c r="D11" s="65"/>
-      <c r="E11" s="65"/>
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
       <c r="F11" s="14"/>
       <c r="G11" s="15" t="s">
         <v>27</v>
@@ -1296,10 +1373,10 @@
       <c r="H11" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="I11" s="54" t="s">
+      <c r="I11" s="47" t="s">
         <v>29</v>
       </c>
-      <c r="J11" s="65"/>
+      <c r="J11" s="53"/>
       <c r="K11" s="31"/>
       <c r="M11" s="10" t="s">
         <v>30</v>
@@ -1348,53 +1425,53 @@
     </row>
     <row r="13" spans="1:22" ht="11.1" customHeight="1">
       <c r="A13" s="18"/>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="53"/>
-      <c r="D13" s="53"/>
-      <c r="E13" s="53"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="53"/>
-      <c r="H13" s="53"/>
-      <c r="I13" s="54" t="s">
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="46"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="47" t="s">
         <v>44</v>
       </c>
-      <c r="J13" s="55"/>
+      <c r="J13" s="48"/>
       <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:22" ht="11.1" customHeight="1">
       <c r="A14" s="19"/>
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="53"/>
-      <c r="D14" s="53"/>
-      <c r="E14" s="53"/>
-      <c r="F14" s="53"/>
-      <c r="G14" s="53"/>
-      <c r="H14" s="53"/>
-      <c r="I14" s="54" t="s">
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="47" t="s">
         <v>47</v>
       </c>
-      <c r="J14" s="55"/>
+      <c r="J14" s="48"/>
       <c r="K14" s="24"/>
     </row>
     <row r="15" spans="1:22" ht="11.1" customHeight="1">
       <c r="A15" s="19"/>
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C15" s="53"/>
-      <c r="D15" s="53"/>
-      <c r="E15" s="53"/>
-      <c r="F15" s="53"/>
-      <c r="G15" s="53"/>
-      <c r="H15" s="53"/>
-      <c r="I15" s="54" t="s">
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="47" t="s">
         <v>48</v>
       </c>
-      <c r="J15" s="55"/>
+      <c r="J15" s="48"/>
       <c r="K15" s="24"/>
       <c r="M15" s="12" t="s">
         <v>36</v>
@@ -1405,19 +1482,19 @@
     </row>
     <row r="16" spans="1:22" ht="11.1" customHeight="1">
       <c r="A16" s="19"/>
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="46" t="s">
         <v>59</v>
       </c>
-      <c r="C16" s="53"/>
-      <c r="D16" s="53"/>
-      <c r="E16" s="53"/>
-      <c r="F16" s="53"/>
-      <c r="G16" s="53"/>
-      <c r="H16" s="53"/>
-      <c r="I16" s="54" t="s">
+      <c r="C16" s="46"/>
+      <c r="D16" s="46"/>
+      <c r="E16" s="46"/>
+      <c r="F16" s="46"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="46"/>
+      <c r="I16" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="55"/>
+      <c r="J16" s="48"/>
       <c r="K16" s="24"/>
       <c r="M16" s="12" t="s">
         <v>34</v>
@@ -1440,19 +1517,19 @@
     </row>
     <row r="17" spans="1:22" ht="11.1" customHeight="1">
       <c r="A17" s="19"/>
-      <c r="B17" s="53" t="s">
+      <c r="B17" s="46" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="53"/>
-      <c r="D17" s="53"/>
-      <c r="E17" s="53"/>
-      <c r="F17" s="53"/>
-      <c r="G17" s="53"/>
-      <c r="H17" s="53"/>
-      <c r="I17" s="54" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="47" t="s">
         <v>49</v>
       </c>
-      <c r="J17" s="55"/>
+      <c r="J17" s="48"/>
       <c r="K17" s="24"/>
       <c r="M17" s="12" t="s">
         <v>34</v>
@@ -1461,7 +1538,7 @@
         <v>61</v>
       </c>
       <c r="O17" s="12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P17" s="3" t="s">
         <v>35</v>
@@ -1482,17 +1559,17 @@
     </row>
     <row r="19" spans="1:22" ht="11.1" customHeight="1">
       <c r="A19" s="25"/>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="62" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="57"/>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="58"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="64"/>
       <c r="K19" s="32"/>
     </row>
     <row r="20" spans="1:22" ht="11.1" customHeight="1">
@@ -1508,39 +1585,46 @@
       <c r="J20" s="33"/>
       <c r="K20" s="32"/>
     </row>
-    <row r="21" spans="1:22" ht="107.1" customHeight="1">
+    <row r="21" spans="1:22" ht="93" customHeight="1">
       <c r="C21" s="40" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="41"/>
+      <c r="F21" s="40" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="42"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="41"/>
+    </row>
+    <row r="22" spans="1:22" ht="30.6" customHeight="1">
+      <c r="C22" s="65" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="66"/>
+      <c r="E22" s="67"/>
+      <c r="F22" s="65" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="40" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="41.45" customHeight="1">
-      <c r="C22" s="42" t="s">
-        <v>71</v>
-      </c>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="43" t="s">
-        <v>74</v>
-      </c>
-      <c r="G22" s="44"/>
-      <c r="H22" s="44"/>
-      <c r="M22" s="12" t="s">
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="I22" s="66"/>
+    </row>
+    <row r="23" spans="1:22" ht="11.1" customHeight="1">
+      <c r="M23" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N22" s="12" t="s">
+      <c r="N23" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="T22" s="8" t="s">
+      <c r="T23" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="U22" s="8" t="s">
+      <c r="U23" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="V22" s="8">
-        <v>23</v>
+      <c r="V23" s="8">
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="11.1" customHeight="1">
@@ -1554,9 +1638,6 @@
       <c r="I24" s="13"/>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
-      <c r="M24" s="38" t="s">
-        <v>69</v>
-      </c>
     </row>
     <row r="25" spans="1:22" ht="11.1" customHeight="1">
       <c r="B25" s="13"/>
@@ -1575,6 +1656,9 @@
     </row>
     <row r="27" spans="1:22" ht="11.1" customHeight="1">
       <c r="B27" s="13"/>
+      <c r="M27" s="38" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="28" spans="1:22" ht="11.1" customHeight="1">
       <c r="B28" s="13"/>
@@ -1632,121 +1716,121 @@
     </row>
     <row r="46" spans="2:6" ht="11.1" customHeight="1">
       <c r="B46" s="13"/>
-      <c r="C46" s="66" t="s">
+      <c r="C46" s="43" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="66"/>
-      <c r="E46" s="66"/>
-      <c r="F46" s="66"/>
+      <c r="D46" s="43"/>
+      <c r="E46" s="43"/>
+      <c r="F46" s="43"/>
     </row>
     <row r="47" spans="2:6" ht="11.1" customHeight="1">
       <c r="B47" s="13"/>
-      <c r="C47" s="66"/>
-      <c r="D47" s="66"/>
-      <c r="E47" s="66"/>
-      <c r="F47" s="66"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="43"/>
+      <c r="F47" s="43"/>
     </row>
     <row r="48" spans="2:6" ht="11.1" customHeight="1">
       <c r="B48" s="13"/>
-      <c r="C48" s="66" t="s">
+      <c r="C48" s="43" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="66"/>
-      <c r="E48" s="66"/>
-      <c r="F48" s="66"/>
+      <c r="D48" s="43"/>
+      <c r="E48" s="43"/>
+      <c r="F48" s="43"/>
     </row>
     <row r="49" spans="2:6" ht="11.1" customHeight="1">
       <c r="B49" s="13"/>
-      <c r="C49" s="66"/>
-      <c r="D49" s="66"/>
-      <c r="E49" s="66"/>
-      <c r="F49" s="66"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="43"/>
+      <c r="E49" s="43"/>
+      <c r="F49" s="43"/>
     </row>
     <row r="50" spans="2:6" ht="11.1" customHeight="1">
       <c r="B50" s="13"/>
-      <c r="C50" s="66" t="s">
+      <c r="C50" s="43" t="s">
         <v>68</v>
       </c>
-      <c r="D50" s="66"/>
-      <c r="E50" s="66"/>
-      <c r="F50" s="66"/>
+      <c r="D50" s="43"/>
+      <c r="E50" s="43"/>
+      <c r="F50" s="43"/>
     </row>
     <row r="51" spans="2:6" ht="11.1" customHeight="1">
       <c r="B51" s="13"/>
-      <c r="C51" s="66"/>
-      <c r="D51" s="66"/>
-      <c r="E51" s="66"/>
-      <c r="F51" s="66"/>
+      <c r="C51" s="43"/>
+      <c r="D51" s="43"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
     </row>
     <row r="52" spans="2:6" ht="11.1" customHeight="1">
       <c r="B52" s="13"/>
-      <c r="C52" s="66"/>
-      <c r="D52" s="66"/>
-      <c r="E52" s="66"/>
-      <c r="F52" s="66"/>
+      <c r="C52" s="43"/>
+      <c r="D52" s="43"/>
+      <c r="E52" s="43"/>
+      <c r="F52" s="43"/>
     </row>
     <row r="53" spans="2:6" ht="11.1" customHeight="1">
       <c r="B53" s="13"/>
-      <c r="C53" s="66"/>
-      <c r="D53" s="66"/>
-      <c r="E53" s="66"/>
-      <c r="F53" s="66"/>
+      <c r="C53" s="43"/>
+      <c r="D53" s="43"/>
+      <c r="E53" s="43"/>
+      <c r="F53" s="43"/>
     </row>
     <row r="54" spans="2:6" ht="11.1" customHeight="1">
       <c r="B54" s="13"/>
-      <c r="C54" s="66"/>
-      <c r="D54" s="66"/>
-      <c r="E54" s="66"/>
-      <c r="F54" s="66"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="43"/>
+      <c r="F54" s="43"/>
     </row>
     <row r="55" spans="2:6" ht="11.1" customHeight="1">
       <c r="B55" s="13"/>
-      <c r="C55" s="66"/>
-      <c r="D55" s="66"/>
-      <c r="E55" s="66"/>
-      <c r="F55" s="66"/>
+      <c r="C55" s="43"/>
+      <c r="D55" s="43"/>
+      <c r="E55" s="43"/>
+      <c r="F55" s="43"/>
     </row>
     <row r="56" spans="2:6" ht="11.1" customHeight="1">
       <c r="B56" s="13"/>
-      <c r="C56" s="66"/>
-      <c r="D56" s="66"/>
-      <c r="E56" s="66"/>
-      <c r="F56" s="66"/>
+      <c r="C56" s="43"/>
+      <c r="D56" s="43"/>
+      <c r="E56" s="43"/>
+      <c r="F56" s="43"/>
     </row>
     <row r="57" spans="2:6" ht="11.1" customHeight="1">
       <c r="B57" s="13"/>
-      <c r="C57" s="66"/>
-      <c r="D57" s="66"/>
-      <c r="E57" s="66"/>
-      <c r="F57" s="66"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="43"/>
+      <c r="F57" s="43"/>
     </row>
     <row r="58" spans="2:6" ht="11.1" customHeight="1">
       <c r="B58" s="13"/>
-      <c r="C58" s="66"/>
-      <c r="D58" s="66"/>
-      <c r="E58" s="66"/>
-      <c r="F58" s="66"/>
+      <c r="C58" s="43"/>
+      <c r="D58" s="43"/>
+      <c r="E58" s="43"/>
+      <c r="F58" s="43"/>
     </row>
     <row r="59" spans="2:6" ht="11.1" customHeight="1">
       <c r="B59" s="13"/>
-      <c r="C59" s="66"/>
-      <c r="D59" s="66"/>
-      <c r="E59" s="66"/>
-      <c r="F59" s="66"/>
+      <c r="C59" s="43"/>
+      <c r="D59" s="43"/>
+      <c r="E59" s="43"/>
+      <c r="F59" s="43"/>
     </row>
     <row r="60" spans="2:6" ht="11.1" customHeight="1">
       <c r="B60" s="13"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="66"/>
+      <c r="C60" s="43"/>
+      <c r="D60" s="43"/>
+      <c r="E60" s="43"/>
+      <c r="F60" s="43"/>
     </row>
     <row r="61" spans="2:6" ht="11.1" customHeight="1">
       <c r="B61" s="13"/>
-      <c r="C61" s="66"/>
-      <c r="D61" s="66"/>
-      <c r="E61" s="66"/>
-      <c r="F61" s="66"/>
+      <c r="C61" s="43"/>
+      <c r="D61" s="43"/>
+      <c r="E61" s="43"/>
+      <c r="F61" s="43"/>
     </row>
     <row r="62" spans="2:6" ht="11.1" customHeight="1">
       <c r="B62" s="13"/>
@@ -1758,27 +1842,8 @@
       <c r="B64" s="13"/>
     </row>
   </sheetData>
-  <mergeCells count="34">
-    <mergeCell ref="C56:F57"/>
-    <mergeCell ref="C58:F59"/>
-    <mergeCell ref="C60:F61"/>
-    <mergeCell ref="C46:F47"/>
-    <mergeCell ref="C48:F49"/>
-    <mergeCell ref="C50:F51"/>
-    <mergeCell ref="C52:F53"/>
-    <mergeCell ref="C54:F55"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="B15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="B11:E11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="F22:H22"/>
+  <mergeCells count="35">
+    <mergeCell ref="F22:I22"/>
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="C2:J3"/>
     <mergeCell ref="H8:H9"/>
@@ -1793,6 +1858,26 @@
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="I17:J17"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="B15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B13:H13"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="C56:F57"/>
+    <mergeCell ref="C58:F59"/>
+    <mergeCell ref="C60:F61"/>
+    <mergeCell ref="C46:F47"/>
+    <mergeCell ref="C48:F49"/>
+    <mergeCell ref="C50:F51"/>
+    <mergeCell ref="C52:F53"/>
+    <mergeCell ref="C54:F55"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.19685039370078741" top="0.27559055118110237" bottom="0.27559055118110237" header="0" footer="0"/>
   <pageSetup paperSize="9" scale="46" fitToHeight="10000" orientation="portrait" r:id="rId1"/>
